--- a/KatalonData/RADTestData/JointFilerSSNZeroError.xlsx
+++ b/KatalonData/RADTestData/JointFilerSSNZeroError.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="73">
   <si>
     <t>Result</t>
   </si>
@@ -246,6 +246,15 @@
   </si>
   <si>
     <t>Fri Oct 02 19:22:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:24:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:24:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:24:34 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -652,7 +661,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -669,7 +678,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -686,7 +695,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
